--- a/data/Blumenau/Setembro 2025 - Angeloni.xlsx
+++ b/data/Blumenau/Setembro 2025 - Angeloni.xlsx
@@ -1,11 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A3204356-52DD-4C60-962B-DFB5887BC997}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://furb-my.sharepoint.com/personal/bttomio_furb_br/Documents/Documentos/GitHub/CidadaniaFinanceira/data/Blumenau/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="3" documentId="8_{A3204356-52DD-4C60-962B-DFB5887BC997}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9CFB7F44-6EF9-49AB-8AAF-9E3B56DC5877}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3360" yWindow="2055" windowWidth="13710" windowHeight="9270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dados" sheetId="1" r:id="rId1"/>
@@ -42,9 +47,6 @@
     <t>DATA</t>
   </si>
   <si>
-    <t>Setembro/ 2025</t>
-  </si>
-  <si>
     <t>Produto</t>
   </si>
   <si>
@@ -223,6 +225,9 @@
   </si>
   <si>
     <t>Caturra</t>
+  </si>
+  <si>
+    <t>Setembro/2025</t>
   </si>
 </sst>
 </file>
@@ -232,7 +237,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.000"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -784,16 +789,67 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -802,73 +858,22 @@
     <xf numFmtId="49" fontId="3" fillId="5" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="3" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1209,7 +1214,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:I32"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15.75"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.85546875" style="4" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.5703125" style="4" bestFit="1" customWidth="1"/>
@@ -1224,7 +1229,7 @@
     <col min="14" max="16384" width="8.7109375" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="18"/>
       <c r="B1" s="19"/>
       <c r="C1" s="19"/>
@@ -1235,7 +1240,7 @@
       <c r="H1" s="19"/>
       <c r="I1" s="21"/>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="22"/>
       <c r="B2" s="23"/>
       <c r="C2" s="23"/>
@@ -1246,7 +1251,7 @@
       <c r="H2" s="23"/>
       <c r="I2" s="25"/>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="22"/>
       <c r="B3" s="23"/>
       <c r="C3" s="23"/>
@@ -1257,7 +1262,7 @@
       <c r="H3" s="23"/>
       <c r="I3" s="25"/>
     </row>
-    <row r="4" spans="1:9" ht="16.5" thickBot="1">
+    <row r="4" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="26"/>
       <c r="B4" s="27"/>
       <c r="C4" s="27"/>
@@ -1268,134 +1273,134 @@
       <c r="H4" s="27"/>
       <c r="I4" s="29"/>
     </row>
-    <row r="5" spans="1:9" ht="16.5" thickBot="1">
+    <row r="5" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="30" t="s">
         <v>0</v>
       </c>
-      <c r="B5" s="40" t="s">
+      <c r="B5" s="57" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="40"/>
+      <c r="C5" s="57"/>
       <c r="D5" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="E5" s="41" t="s">
-        <v>3</v>
-      </c>
-      <c r="F5" s="41"/>
-      <c r="G5" s="41"/>
+      <c r="E5" s="58" t="s">
+        <v>63</v>
+      </c>
+      <c r="F5" s="58"/>
+      <c r="G5" s="58"/>
       <c r="H5" s="16"/>
       <c r="I5" s="17"/>
     </row>
-    <row r="6" spans="1:9" ht="16.5" thickBot="1">
+    <row r="6" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="C6" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="D6" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="E6" s="61" t="s">
         <v>7</v>
       </c>
-      <c r="E6" s="42" t="s">
+      <c r="F6" s="62"/>
+      <c r="G6" s="62"/>
+      <c r="H6" s="62"/>
+      <c r="I6" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F6" s="43"/>
-      <c r="G6" s="43"/>
-      <c r="H6" s="43"/>
-      <c r="I6" s="3" t="s">
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" s="36" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="7" spans="1:9">
-      <c r="A7" s="63" t="s">
+      <c r="B7" s="38" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="46" t="s">
+      <c r="C7" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="46" t="s">
+      <c r="D7" s="40">
+        <v>1</v>
+      </c>
+      <c r="E7" s="32" t="s">
         <v>12</v>
       </c>
-      <c r="D7" s="44">
-        <v>1</v>
-      </c>
-      <c r="E7" s="32" t="s">
+      <c r="F7" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F7" s="5" t="s">
+      <c r="G7" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="G7" s="5" t="s">
+      <c r="H7" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="H7" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="I7" s="36">
+      <c r="I7" s="59">
         <f>AVERAGE(F8:H8)</f>
         <v>3.44</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="16.5" thickBot="1">
-      <c r="A8" s="64"/>
-      <c r="B8" s="47"/>
-      <c r="C8" s="47"/>
-      <c r="D8" s="45"/>
+    <row r="8" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="37"/>
+      <c r="B8" s="39"/>
+      <c r="C8" s="39"/>
+      <c r="D8" s="41"/>
       <c r="E8" s="33" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F8" s="7">
         <v>3.29</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H8" s="8">
         <v>3.59</v>
       </c>
-      <c r="I8" s="37"/>
-    </row>
-    <row r="9" spans="1:9">
-      <c r="A9" s="56" t="s">
+      <c r="I8" s="60"/>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" s="42" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9" s="44" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9" s="44" t="s">
+        <v>11</v>
+      </c>
+      <c r="D9" s="46">
+        <v>1</v>
+      </c>
+      <c r="E9" s="34" t="s">
+        <v>12</v>
+      </c>
+      <c r="F9" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="B9" s="54" t="s">
-        <v>11</v>
-      </c>
-      <c r="C9" s="54" t="s">
-        <v>12</v>
-      </c>
-      <c r="D9" s="58">
-        <v>1</v>
-      </c>
-      <c r="E9" s="34" t="s">
-        <v>13</v>
-      </c>
-      <c r="F9" s="9" t="s">
+      <c r="G9" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="G9" s="9" t="s">
+      <c r="H9" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="H9" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="I9" s="38">
+      <c r="I9" s="63">
         <f>AVERAGE(F10:H10)</f>
         <v>4.3900000000000006</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="16.5" thickBot="1">
-      <c r="A10" s="60"/>
-      <c r="B10" s="62"/>
-      <c r="C10" s="62"/>
-      <c r="D10" s="61"/>
+    <row r="10" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="43"/>
+      <c r="B10" s="45"/>
+      <c r="C10" s="45"/>
+      <c r="D10" s="47"/>
       <c r="E10" s="35" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F10" s="11">
         <v>4.29</v>
@@ -1406,45 +1411,45 @@
       <c r="H10" s="12">
         <v>4.3899999999999997</v>
       </c>
-      <c r="I10" s="39"/>
-    </row>
-    <row r="11" spans="1:9">
-      <c r="A11" s="63" t="s">
+      <c r="I10" s="64"/>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" s="36" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11" s="38" t="s">
+        <v>10</v>
+      </c>
+      <c r="C11" s="38" t="s">
+        <v>11</v>
+      </c>
+      <c r="D11" s="40">
+        <v>0.5</v>
+      </c>
+      <c r="E11" s="32" t="s">
+        <v>12</v>
+      </c>
+      <c r="F11" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="B11" s="46" t="s">
-        <v>11</v>
-      </c>
-      <c r="C11" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="D11" s="44">
-        <v>0.5</v>
-      </c>
-      <c r="E11" s="32" t="s">
-        <v>13</v>
-      </c>
-      <c r="F11" s="5" t="s">
+      <c r="G11" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="G11" s="5" t="s">
+      <c r="H11" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="H11" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="I11" s="36">
+      <c r="I11" s="59">
         <f>AVERAGE(F12:H12)</f>
         <v>33.93</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="16.5" thickBot="1">
-      <c r="A12" s="64"/>
-      <c r="B12" s="47"/>
-      <c r="C12" s="47"/>
-      <c r="D12" s="45"/>
+    <row r="12" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="37"/>
+      <c r="B12" s="39"/>
+      <c r="C12" s="39"/>
+      <c r="D12" s="41"/>
       <c r="E12" s="33" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F12" s="7">
         <v>32.99</v>
@@ -1455,45 +1460,45 @@
       <c r="H12" s="8">
         <v>33.9</v>
       </c>
-      <c r="I12" s="37"/>
-    </row>
-    <row r="13" spans="1:9">
-      <c r="A13" s="56" t="s">
+      <c r="I12" s="60"/>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13" s="42" t="s">
+        <v>26</v>
+      </c>
+      <c r="B13" s="44" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13" s="44" t="s">
+        <v>11</v>
+      </c>
+      <c r="D13" s="46">
+        <v>1</v>
+      </c>
+      <c r="E13" s="34" t="s">
         <v>27</v>
       </c>
-      <c r="B13" s="54" t="s">
-        <v>11</v>
-      </c>
-      <c r="C13" s="54" t="s">
-        <v>12</v>
-      </c>
-      <c r="D13" s="58">
-        <v>1</v>
-      </c>
-      <c r="E13" s="34" t="s">
+      <c r="F13" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="F13" s="9" t="s">
+      <c r="G13" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="G13" s="9" t="s">
+      <c r="H13" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="H13" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="I13" s="38">
+      <c r="I13" s="63">
         <f>AVERAGE(F14:H14)</f>
         <v>3.69</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="16.5" thickBot="1">
-      <c r="A14" s="60"/>
-      <c r="B14" s="62"/>
-      <c r="C14" s="62"/>
-      <c r="D14" s="61"/>
+    <row r="14" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="43"/>
+      <c r="B14" s="45"/>
+      <c r="C14" s="45"/>
+      <c r="D14" s="47"/>
       <c r="E14" s="35" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F14" s="11">
         <v>3.59</v>
@@ -1504,45 +1509,45 @@
       <c r="H14" s="12">
         <v>3.19</v>
       </c>
-      <c r="I14" s="39"/>
-    </row>
-    <row r="15" spans="1:9">
-      <c r="A15" s="63" t="s">
+      <c r="I14" s="64"/>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A15" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="B15" s="38" t="s">
+        <v>10</v>
+      </c>
+      <c r="C15" s="38" t="s">
+        <v>11</v>
+      </c>
+      <c r="D15" s="40">
+        <v>1</v>
+      </c>
+      <c r="E15" s="32" t="s">
+        <v>12</v>
+      </c>
+      <c r="F15" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="B15" s="46" t="s">
-        <v>11</v>
-      </c>
-      <c r="C15" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="D15" s="44">
-        <v>1</v>
-      </c>
-      <c r="E15" s="32" t="s">
-        <v>13</v>
-      </c>
-      <c r="F15" s="5" t="s">
+      <c r="G15" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="G15" s="5" t="s">
+      <c r="H15" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="H15" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="I15" s="36">
+      <c r="I15" s="59">
         <f>AVERAGE(F16:H16)</f>
         <v>4.9233333333333338</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="16.5" thickBot="1">
-      <c r="A16" s="64"/>
-      <c r="B16" s="47"/>
-      <c r="C16" s="47"/>
-      <c r="D16" s="45"/>
+    <row r="16" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="37"/>
+      <c r="B16" s="39"/>
+      <c r="C16" s="39"/>
+      <c r="D16" s="41"/>
       <c r="E16" s="33" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F16" s="7">
         <v>4.79</v>
@@ -1553,45 +1558,45 @@
       <c r="H16" s="8">
         <v>4.99</v>
       </c>
-      <c r="I16" s="37"/>
-    </row>
-    <row r="17" spans="1:9">
-      <c r="A17" s="56" t="s">
+      <c r="I16" s="60"/>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A17" s="42" t="s">
+        <v>35</v>
+      </c>
+      <c r="B17" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="B17" s="54" t="s">
+      <c r="C17" s="44" t="s">
+        <v>11</v>
+      </c>
+      <c r="D17" s="46">
+        <v>0.5</v>
+      </c>
+      <c r="E17" s="34" t="s">
+        <v>12</v>
+      </c>
+      <c r="F17" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="C17" s="54" t="s">
-        <v>12</v>
-      </c>
-      <c r="D17" s="58">
-        <v>0.5</v>
-      </c>
-      <c r="E17" s="34" t="s">
-        <v>13</v>
-      </c>
-      <c r="F17" s="9" t="s">
+      <c r="G17" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="G17" s="9" t="s">
+      <c r="H17" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="H17" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="I17" s="38">
+      <c r="I17" s="63">
         <f>AVERAGE(F18:H18)</f>
         <v>34.633333333333333</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="16.5" thickBot="1">
-      <c r="A18" s="60"/>
-      <c r="B18" s="62"/>
-      <c r="C18" s="62"/>
-      <c r="D18" s="61"/>
+    <row r="18" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="43"/>
+      <c r="B18" s="45"/>
+      <c r="C18" s="45"/>
+      <c r="D18" s="47"/>
       <c r="E18" s="35" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F18" s="11">
         <v>32.450000000000003</v>
@@ -1602,43 +1607,43 @@
       <c r="H18" s="12">
         <v>36.25</v>
       </c>
-      <c r="I18" s="39"/>
-    </row>
-    <row r="19" spans="1:9">
-      <c r="A19" s="63" t="s">
+      <c r="I18" s="64"/>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A19" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="B19" s="38" t="s">
         <v>41</v>
       </c>
-      <c r="B19" s="46" t="s">
+      <c r="C19" s="38" t="s">
         <v>42</v>
       </c>
-      <c r="C19" s="46" t="s">
+      <c r="D19" s="40">
+        <v>0.9</v>
+      </c>
+      <c r="E19" s="32" t="s">
+        <v>12</v>
+      </c>
+      <c r="F19" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="D19" s="44">
-        <v>0.9</v>
-      </c>
-      <c r="E19" s="32" t="s">
-        <v>13</v>
-      </c>
-      <c r="F19" s="5" t="s">
+      <c r="G19" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="G19" s="5" t="s">
-        <v>45</v>
-      </c>
       <c r="H19" s="6"/>
-      <c r="I19" s="36">
+      <c r="I19" s="59">
         <f>AVERAGE(F20:H20)</f>
         <v>7.2200000000000006</v>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="16.5" thickBot="1">
-      <c r="A20" s="64"/>
-      <c r="B20" s="47"/>
-      <c r="C20" s="47"/>
-      <c r="D20" s="45"/>
+    <row r="20" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="37"/>
+      <c r="B20" s="39"/>
+      <c r="C20" s="39"/>
+      <c r="D20" s="41"/>
       <c r="E20" s="33" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F20" s="7">
         <v>7.25</v>
@@ -1647,45 +1652,45 @@
         <v>7.19</v>
       </c>
       <c r="H20" s="8"/>
-      <c r="I20" s="37"/>
-    </row>
-    <row r="21" spans="1:9">
-      <c r="A21" s="56" t="s">
+      <c r="I20" s="60"/>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A21" s="42" t="s">
+        <v>45</v>
+      </c>
+      <c r="B21" s="44" t="s">
         <v>46</v>
       </c>
-      <c r="B21" s="54" t="s">
+      <c r="C21" s="44" t="s">
+        <v>11</v>
+      </c>
+      <c r="D21" s="46">
+        <v>1</v>
+      </c>
+      <c r="E21" s="34" t="s">
+        <v>12</v>
+      </c>
+      <c r="F21" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="C21" s="54" t="s">
-        <v>12</v>
-      </c>
-      <c r="D21" s="58">
-        <v>1</v>
-      </c>
-      <c r="E21" s="34" t="s">
-        <v>13</v>
-      </c>
-      <c r="F21" s="9" t="s">
+      <c r="G21" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="G21" s="9" t="s">
+      <c r="H21" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="H21" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="I21" s="38">
+      <c r="I21" s="63">
         <f>AVERAGE(F22:H22)</f>
         <v>57.233333333333327</v>
       </c>
     </row>
-    <row r="22" spans="1:9" ht="16.5" thickBot="1">
-      <c r="A22" s="60"/>
-      <c r="B22" s="62"/>
-      <c r="C22" s="62"/>
-      <c r="D22" s="61"/>
+    <row r="22" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="43"/>
+      <c r="B22" s="45"/>
+      <c r="C22" s="45"/>
+      <c r="D22" s="47"/>
       <c r="E22" s="35" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F22" s="11">
         <v>53.9</v>
@@ -1696,168 +1701,163 @@
       <c r="H22" s="12">
         <v>54.9</v>
       </c>
-      <c r="I22" s="39"/>
-    </row>
-    <row r="23" spans="1:9">
-      <c r="A23" s="63" t="s">
+      <c r="I22" s="64"/>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A23" s="36" t="s">
+        <v>50</v>
+      </c>
+      <c r="B23" s="38" t="s">
+        <v>46</v>
+      </c>
+      <c r="C23" s="38" t="s">
+        <v>11</v>
+      </c>
+      <c r="D23" s="40">
+        <v>1</v>
+      </c>
+      <c r="E23" s="32" t="s">
+        <v>12</v>
+      </c>
+      <c r="F23" s="5" t="s">
         <v>51</v>
-      </c>
-      <c r="B23" s="46" t="s">
-        <v>47</v>
-      </c>
-      <c r="C23" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="D23" s="44">
-        <v>1</v>
-      </c>
-      <c r="E23" s="32" t="s">
-        <v>13</v>
-      </c>
-      <c r="F23" s="5" t="s">
-        <v>52</v>
       </c>
       <c r="G23" s="5"/>
       <c r="H23" s="6"/>
-      <c r="I23" s="36">
+      <c r="I23" s="59">
         <f>AVERAGE(F24:H24)</f>
         <v>16.5</v>
       </c>
     </row>
-    <row r="24" spans="1:9" ht="16.5" thickBot="1">
-      <c r="A24" s="64"/>
-      <c r="B24" s="47"/>
-      <c r="C24" s="47"/>
-      <c r="D24" s="45"/>
+    <row r="24" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="37"/>
+      <c r="B24" s="39"/>
+      <c r="C24" s="39"/>
+      <c r="D24" s="41"/>
       <c r="E24" s="33" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F24" s="7">
         <v>16.5</v>
       </c>
       <c r="G24" s="7"/>
       <c r="H24" s="8"/>
-      <c r="I24" s="37"/>
-    </row>
-    <row r="25" spans="1:9">
-      <c r="A25" s="56" t="s">
+      <c r="I24" s="60"/>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A25" s="42" t="s">
+        <v>52</v>
+      </c>
+      <c r="B25" s="44" t="s">
+        <v>46</v>
+      </c>
+      <c r="C25" s="44" t="s">
+        <v>11</v>
+      </c>
+      <c r="D25" s="46">
+        <v>1</v>
+      </c>
+      <c r="E25" s="34" t="s">
+        <v>12</v>
+      </c>
+      <c r="F25" s="9" t="s">
         <v>53</v>
-      </c>
-      <c r="B25" s="54" t="s">
-        <v>47</v>
-      </c>
-      <c r="C25" s="54" t="s">
-        <v>12</v>
-      </c>
-      <c r="D25" s="58">
-        <v>1</v>
-      </c>
-      <c r="E25" s="34" t="s">
-        <v>13</v>
-      </c>
-      <c r="F25" s="9" t="s">
-        <v>54</v>
       </c>
       <c r="G25" s="9"/>
       <c r="H25" s="10"/>
-      <c r="I25" s="38">
-        <f>AVERAGE(F26:H26)</f>
-        <v>1.99</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" ht="16.5" thickBot="1">
-      <c r="A26" s="60"/>
-      <c r="B26" s="62"/>
-      <c r="C26" s="62"/>
-      <c r="D26" s="61"/>
+      <c r="I25" s="63"/>
+    </row>
+    <row r="26" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="43"/>
+      <c r="B26" s="45"/>
+      <c r="C26" s="45"/>
+      <c r="D26" s="47"/>
       <c r="E26" s="35" t="s">
-        <v>17</v>
-      </c>
-      <c r="F26" s="11">
-        <v>1.99</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="F26" s="11"/>
       <c r="G26" s="11"/>
       <c r="H26" s="12"/>
-      <c r="I26" s="39"/>
-    </row>
-    <row r="27" spans="1:9">
-      <c r="A27" s="48" t="s">
+      <c r="I26" s="64"/>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A27" s="52" t="s">
+        <v>54</v>
+      </c>
+      <c r="B27" s="48" t="s">
+        <v>46</v>
+      </c>
+      <c r="C27" s="48" t="s">
+        <v>11</v>
+      </c>
+      <c r="D27" s="50">
+        <v>1</v>
+      </c>
+      <c r="E27" s="32" t="s">
+        <v>12</v>
+      </c>
+      <c r="F27" s="5" t="s">
         <v>55</v>
-      </c>
-      <c r="B27" s="50" t="s">
-        <v>47</v>
-      </c>
-      <c r="C27" s="50" t="s">
-        <v>12</v>
-      </c>
-      <c r="D27" s="52">
-        <v>1</v>
-      </c>
-      <c r="E27" s="32" t="s">
-        <v>13</v>
-      </c>
-      <c r="F27" s="5" t="s">
-        <v>56</v>
       </c>
       <c r="G27" s="5"/>
       <c r="H27" s="6"/>
-      <c r="I27" s="36">
+      <c r="I27" s="59">
         <f>AVERAGE(F28:H28)</f>
         <v>8.99</v>
       </c>
     </row>
-    <row r="28" spans="1:9" ht="16.5" thickBot="1">
-      <c r="A28" s="49"/>
-      <c r="B28" s="51"/>
-      <c r="C28" s="51"/>
-      <c r="D28" s="53"/>
+    <row r="28" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="53"/>
+      <c r="B28" s="49"/>
+      <c r="C28" s="49"/>
+      <c r="D28" s="51"/>
       <c r="E28" s="33" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F28" s="7">
         <v>8.99</v>
       </c>
       <c r="G28" s="7"/>
       <c r="H28" s="8"/>
-      <c r="I28" s="37"/>
-    </row>
-    <row r="29" spans="1:9">
-      <c r="A29" s="56" t="s">
+      <c r="I28" s="60"/>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A29" s="42" t="s">
+        <v>56</v>
+      </c>
+      <c r="B29" s="44" t="s">
         <v>57</v>
       </c>
-      <c r="B29" s="54" t="s">
+      <c r="C29" s="44" t="s">
+        <v>42</v>
+      </c>
+      <c r="D29" s="46">
+        <v>1</v>
+      </c>
+      <c r="E29" s="34" t="s">
+        <v>12</v>
+      </c>
+      <c r="F29" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="C29" s="54" t="s">
-        <v>43</v>
-      </c>
-      <c r="D29" s="58">
-        <v>1</v>
-      </c>
-      <c r="E29" s="34" t="s">
-        <v>13</v>
-      </c>
-      <c r="F29" s="9" t="s">
+      <c r="G29" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="G29" s="9" t="s">
+      <c r="H29" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="H29" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="I29" s="38">
+      <c r="I29" s="63">
         <f>AVERAGE(F30:H30)</f>
         <v>4.3899999999999997</v>
       </c>
     </row>
-    <row r="30" spans="1:9" ht="16.5" thickBot="1">
-      <c r="A30" s="57"/>
-      <c r="B30" s="55"/>
-      <c r="C30" s="55"/>
-      <c r="D30" s="59"/>
+    <row r="30" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="55"/>
+      <c r="B30" s="54"/>
+      <c r="C30" s="54"/>
+      <c r="D30" s="56"/>
       <c r="E30" s="33" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F30" s="13">
         <v>4.09</v>
@@ -1868,64 +1868,90 @@
       <c r="H30" s="14">
         <v>4.49</v>
       </c>
-      <c r="I30" s="39"/>
-    </row>
-    <row r="31" spans="1:9">
-      <c r="A31" s="48" t="s">
+      <c r="I30" s="64"/>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A31" s="52" t="s">
+        <v>61</v>
+      </c>
+      <c r="B31" s="48" t="s">
+        <v>46</v>
+      </c>
+      <c r="C31" s="48" t="s">
+        <v>11</v>
+      </c>
+      <c r="D31" s="50">
+        <v>1</v>
+      </c>
+      <c r="E31" s="32" t="s">
+        <v>12</v>
+      </c>
+      <c r="F31" s="5" t="s">
         <v>62</v>
-      </c>
-      <c r="B31" s="50" t="s">
-        <v>47</v>
-      </c>
-      <c r="C31" s="50" t="s">
-        <v>12</v>
-      </c>
-      <c r="D31" s="52">
-        <v>1</v>
-      </c>
-      <c r="E31" s="32" t="s">
-        <v>13</v>
-      </c>
-      <c r="F31" s="5" t="s">
-        <v>63</v>
       </c>
       <c r="G31" s="5"/>
       <c r="H31" s="6"/>
-      <c r="I31" s="36">
+      <c r="I31" s="59">
         <f>AVERAGE(F32:H32)</f>
         <v>4.99</v>
       </c>
     </row>
-    <row r="32" spans="1:9" ht="16.5" thickBot="1">
-      <c r="A32" s="49"/>
-      <c r="B32" s="51"/>
-      <c r="C32" s="51"/>
-      <c r="D32" s="53"/>
+    <row r="32" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="53"/>
+      <c r="B32" s="49"/>
+      <c r="C32" s="49"/>
+      <c r="D32" s="51"/>
       <c r="E32" s="33" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F32" s="7">
         <v>4.99</v>
       </c>
       <c r="G32" s="7"/>
       <c r="H32" s="8"/>
-      <c r="I32" s="37"/>
+      <c r="I32" s="60"/>
     </row>
   </sheetData>
   <mergeCells count="68">
-    <mergeCell ref="A7:A8"/>
-    <mergeCell ref="B7:B8"/>
-    <mergeCell ref="C7:C8"/>
-    <mergeCell ref="D7:D8"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="B9:B10"/>
-    <mergeCell ref="C9:C10"/>
-    <mergeCell ref="D9:D10"/>
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="B13:B14"/>
-    <mergeCell ref="C13:C14"/>
-    <mergeCell ref="D13:D14"/>
+    <mergeCell ref="I19:I20"/>
+    <mergeCell ref="I23:I24"/>
+    <mergeCell ref="I27:I28"/>
+    <mergeCell ref="I31:I32"/>
+    <mergeCell ref="I9:I10"/>
+    <mergeCell ref="I13:I14"/>
+    <mergeCell ref="I17:I18"/>
+    <mergeCell ref="I21:I22"/>
+    <mergeCell ref="I25:I26"/>
+    <mergeCell ref="I29:I30"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="E5:G5"/>
+    <mergeCell ref="I7:I8"/>
+    <mergeCell ref="I11:I12"/>
+    <mergeCell ref="I15:I16"/>
+    <mergeCell ref="E6:H6"/>
+    <mergeCell ref="D11:D12"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="A31:A32"/>
+    <mergeCell ref="B31:B32"/>
+    <mergeCell ref="C31:C32"/>
+    <mergeCell ref="D31:D32"/>
+    <mergeCell ref="C29:C30"/>
+    <mergeCell ref="A29:A30"/>
+    <mergeCell ref="D29:D30"/>
+    <mergeCell ref="B29:B30"/>
+    <mergeCell ref="A25:A26"/>
+    <mergeCell ref="C27:C28"/>
+    <mergeCell ref="D17:D18"/>
+    <mergeCell ref="D19:D20"/>
+    <mergeCell ref="D21:D22"/>
+    <mergeCell ref="D23:D24"/>
+    <mergeCell ref="D25:D26"/>
+    <mergeCell ref="C17:C18"/>
+    <mergeCell ref="C19:C20"/>
+    <mergeCell ref="C21:C22"/>
+    <mergeCell ref="C23:C24"/>
+    <mergeCell ref="C25:C26"/>
     <mergeCell ref="A15:A16"/>
     <mergeCell ref="B15:B16"/>
     <mergeCell ref="C15:C16"/>
@@ -1942,45 +1968,19 @@
     <mergeCell ref="A19:A20"/>
     <mergeCell ref="A21:A22"/>
     <mergeCell ref="A23:A24"/>
-    <mergeCell ref="A25:A26"/>
-    <mergeCell ref="C27:C28"/>
-    <mergeCell ref="D17:D18"/>
-    <mergeCell ref="D19:D20"/>
-    <mergeCell ref="D21:D22"/>
-    <mergeCell ref="D23:D24"/>
-    <mergeCell ref="D25:D26"/>
-    <mergeCell ref="C17:C18"/>
-    <mergeCell ref="C19:C20"/>
-    <mergeCell ref="C21:C22"/>
-    <mergeCell ref="C23:C24"/>
-    <mergeCell ref="C25:C26"/>
-    <mergeCell ref="A31:A32"/>
-    <mergeCell ref="B31:B32"/>
-    <mergeCell ref="C31:C32"/>
-    <mergeCell ref="D31:D32"/>
-    <mergeCell ref="C29:C30"/>
-    <mergeCell ref="A29:A30"/>
-    <mergeCell ref="D29:D30"/>
-    <mergeCell ref="B29:B30"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="E5:G5"/>
-    <mergeCell ref="I7:I8"/>
-    <mergeCell ref="I11:I12"/>
-    <mergeCell ref="I15:I16"/>
-    <mergeCell ref="E6:H6"/>
-    <mergeCell ref="D11:D12"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="I19:I20"/>
-    <mergeCell ref="I23:I24"/>
-    <mergeCell ref="I27:I28"/>
-    <mergeCell ref="I31:I32"/>
-    <mergeCell ref="I9:I10"/>
-    <mergeCell ref="I13:I14"/>
-    <mergeCell ref="I17:I18"/>
-    <mergeCell ref="I21:I22"/>
-    <mergeCell ref="I25:I26"/>
-    <mergeCell ref="I29:I30"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="D13:D14"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="C7:C8"/>
+    <mergeCell ref="D7:D8"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="C9:C10"/>
+    <mergeCell ref="D9:D10"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
